--- a/2.RCM/FCRP_RCM.xlsx
+++ b/2.RCM/FCRP_RCM.xlsx
@@ -554,6 +554,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -798,7 +799,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>経理部課長（E0012）が各子会社（東北/物流/タイ/TPT）からアップロードされた連結パッケージを連結決算システム（S05）のバリデーションレポートでチェックし、差異について子会社担当者と往復確認する。</t>
+          <t>経理部課長（E0012）が各子会社（東北/物流/タイ/DAT）からアップロードされた連結パッケージを連結決算システム（S05）のバリデーションレポートでチェックし、差異について子会社担当者と往復確認する。</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -1225,6 +1226,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
